--- a/data/trans_orig/MCS12_SP-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/MCS12_SP-Habitat-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Puntuación media del componente de salud mental (SF12)</t>
+          <t>Puntuación media del componente de salud mental (SF12) (tasa de respuesta: 99,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>52,72; 53,73</t>
+          <t>52,72; 53,67</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>51,78; 52,85</t>
+          <t>51,77; 52,89</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>51,63; 52,91</t>
+          <t>51,67; 52,91</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>52,23; 53,55</t>
+          <t>52,17; 53,47</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>51,43; 52,49</t>
+          <t>51,43; 52,55</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>47,85; 49,49</t>
+          <t>47,82; 49,4</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>49,62; 51,13</t>
+          <t>49,56; 51,04</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>50,94; 51,99</t>
+          <t>50,89; 52,01</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>52,24; 52,96</t>
+          <t>52,21; 52,94</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>50,0; 51,03</t>
+          <t>49,99; 51,01</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>50,82; 51,81</t>
+          <t>50,85; 51,81</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>51,73; 52,63</t>
+          <t>51,77; 52,64</t>
         </is>
       </c>
     </row>
@@ -856,7 +856,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>51,92; 52,84</t>
+          <t>51,87; 52,83</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -866,32 +866,32 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>52,51; 53,33</t>
+          <t>52,47; 53,28</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>52,72; 54,2</t>
+          <t>52,75; 54,22</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>50,03; 51,14</t>
+          <t>50,04; 51,17</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>48,8; 50,05</t>
+          <t>48,7; 50,04</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>50,2; 51,37</t>
+          <t>50,21; 51,41</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>50,24; 51,33</t>
+          <t>50,26; 51,33</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -901,17 +901,17 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>50,2; 51,06</t>
+          <t>50,24; 51,09</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>51,45; 52,23</t>
+          <t>51,47; 52,21</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>51,76; 53,24</t>
+          <t>51,71; 53,26</t>
         </is>
       </c>
     </row>
@@ -1001,57 +1001,57 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>51,97; 53,21</t>
+          <t>51,97; 53,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>52,27; 53,45</t>
+          <t>52,31; 53,39</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>51,41; 52,92</t>
+          <t>51,34; 52,97</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>49,74; 51,16</t>
+          <t>49,76; 51,15</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>49,19; 50,66</t>
+          <t>49,19; 50,69</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>50,3; 51,74</t>
+          <t>50,33; 51,72</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>47,02; 51,3</t>
+          <t>46,84; 51,34</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>51,1; 51,98</t>
+          <t>51,1; 51,99</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>50,81; 51,75</t>
+          <t>50,75; 51,72</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>51,53; 52,42</t>
+          <t>51,52; 52,43</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>48,52; 51,84</t>
+          <t>48,37; 51,78</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>51,6; 52,58</t>
+          <t>51,63; 52,59</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>50,93; 52,03</t>
+          <t>50,97; 52,05</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>51,15; 52,18</t>
+          <t>51,05; 52,16</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>51,95; 53,05</t>
+          <t>51,94; 52,97</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>49,73; 50,86</t>
+          <t>49,68; 50,81</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>48,22; 49,46</t>
+          <t>48,19; 49,42</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>49,53; 50,78</t>
+          <t>49,5; 50,74</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>49,75; 50,91</t>
+          <t>49,75; 51,02</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>50,81; 51,55</t>
+          <t>50,79; 51,56</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>49,71; 50,56</t>
+          <t>49,69; 50,51</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>50,48; 51,3</t>
+          <t>50,49; 51,3</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>50,9; 51,7</t>
+          <t>50,88; 51,7</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>52,31; 52,8</t>
+          <t>52,27; 52,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>51,75; 52,32</t>
+          <t>51,78; 52,36</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>52,17; 52,7</t>
+          <t>52,16; 52,7</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>52,48; 53,31</t>
+          <t>52,48; 53,32</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>50,47; 51,07</t>
+          <t>50,45; 51,07</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>48,86; 49,56</t>
+          <t>48,88; 49,57</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>50,31; 50,93</t>
+          <t>50,27; 50,92</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>49,39; 50,96</t>
+          <t>49,35; 50,95</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>51,45; 51,86</t>
+          <t>51,47; 51,82</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>50,4; 50,84</t>
+          <t>50,38; 50,83</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>51,3; 51,71</t>
+          <t>51,32; 51,71</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>50,98; 51,99</t>
+          <t>50,88; 52,0</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/MCS12_SP-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/MCS12_SP-Habitat-trans_orig.xlsx
@@ -716,17 +716,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>52,72; 53,67</t>
+          <t>52,76; 53,67</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>51,77; 52,89</t>
+          <t>51,67; 52,88</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>51,67; 52,91</t>
+          <t>51,65; 52,89</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -736,42 +736,42 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>51,43; 52,55</t>
+          <t>51,41; 52,55</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>47,82; 49,4</t>
+          <t>47,93; 49,55</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>49,56; 51,04</t>
+          <t>49,6; 51,09</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>50,89; 52,01</t>
+          <t>50,9; 52,02</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>52,21; 52,94</t>
+          <t>52,19; 52,93</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>49,99; 51,01</t>
+          <t>49,98; 50,97</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>50,85; 51,81</t>
+          <t>50,72; 51,81</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>51,77; 52,64</t>
+          <t>51,69; 52,55</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>53,39</t>
+          <t>52,99</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>50,82</t>
+          <t>50,78</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>52,25</t>
+          <t>51,87</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>51,87; 52,83</t>
+          <t>51,92; 52,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>51,38; 52,4</t>
+          <t>51,36; 52,43</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>52,47; 53,28</t>
+          <t>52,46; 53,35</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>52,75; 54,22</t>
+          <t>52,47; 53,45</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>50,04; 51,17</t>
+          <t>50,02; 51,16</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>48,7; 50,04</t>
+          <t>48,65; 50,01</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>50,21; 51,41</t>
+          <t>50,25; 51,47</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>50,26; 51,33</t>
+          <t>50,25; 51,29</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>51,12; 51,84</t>
+          <t>51,13; 51,84</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>50,24; 51,09</t>
+          <t>50,25; 51,08</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>51,47; 52,21</t>
+          <t>51,49; 52,23</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>51,71; 53,26</t>
+          <t>51,5; 52,21</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>52,23</t>
+          <t>52,28</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>49,53</t>
+          <t>50,63</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>50,69</t>
+          <t>51,45</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>52,09; 53,18</t>
+          <t>52,11; 53,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>51,97; 53,25</t>
+          <t>51,99; 53,18</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>52,31; 53,39</t>
+          <t>52,26; 53,44</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>51,34; 52,97</t>
+          <t>51,59; 52,98</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>49,76; 51,15</t>
+          <t>49,78; 51,16</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>49,19; 50,69</t>
+          <t>49,24; 50,68</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>50,33; 51,72</t>
+          <t>50,34; 51,75</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>46,84; 51,34</t>
+          <t>49,95; 51,26</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>51,1; 51,99</t>
+          <t>51,03; 51,96</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>50,75; 51,72</t>
+          <t>50,84; 51,79</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>51,52; 52,43</t>
+          <t>51,53; 52,4</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>48,37; 51,78</t>
+          <t>50,93; 51,89</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>52,47</t>
+          <t>52,38</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>50,32</t>
+          <t>50,1</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>51,31</t>
+          <t>51,17</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>51,63; 52,59</t>
+          <t>51,64; 52,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>50,97; 52,05</t>
+          <t>51,01; 52,03</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>51,05; 52,16</t>
+          <t>51,05; 52,21</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>51,94; 52,97</t>
+          <t>51,9; 52,88</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>49,68; 50,81</t>
+          <t>49,73; 50,83</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>48,19; 49,42</t>
+          <t>48,23; 49,41</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>49,5; 50,74</t>
+          <t>49,55; 50,76</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>49,75; 51,02</t>
+          <t>49,55; 50,55</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>50,79; 51,56</t>
+          <t>50,8; 51,57</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>49,69; 50,51</t>
+          <t>49,66; 50,5</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>50,49; 51,3</t>
+          <t>50,48; 51,27</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>50,88; 51,7</t>
+          <t>50,78; 51,55</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>52,82</t>
+          <t>52,64</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>50,46</t>
+          <t>50,68</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>51,61</t>
+          <t>51,63</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>52,27; 52,77</t>
+          <t>52,29; 52,81</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>51,78; 52,36</t>
+          <t>51,7; 52,3</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>52,16; 52,7</t>
+          <t>52,19; 52,7</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>52,48; 53,32</t>
+          <t>52,35; 52,94</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>50,45; 51,07</t>
+          <t>50,46; 51,07</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>48,88; 49,57</t>
+          <t>48,86; 49,56</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>50,27; 50,92</t>
+          <t>50,27; 50,95</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>49,35; 50,95</t>
+          <t>50,39; 50,99</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>51,47; 51,82</t>
+          <t>51,46; 51,85</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>50,38; 50,83</t>
+          <t>50,39; 50,83</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>51,32; 51,71</t>
+          <t>51,28; 51,71</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>50,88; 52,0</t>
+          <t>51,43; 51,83</t>
         </is>
       </c>
     </row>
